--- a/Thesis Forecasting/PAPER CONTEXT/tables/appendix_I_testing_metrics_summary.xlsx
+++ b/Thesis Forecasting/PAPER CONTEXT/tables/appendix_I_testing_metrics_summary.xlsx
@@ -506,31 +506,31 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>158</v>
+        <v>198</v>
       </c>
       <c r="D2" t="n">
-        <v>3.471231035467674</v>
+        <v>6.153104165758873</v>
       </c>
       <c r="E2" t="n">
-        <v>1.726776719652155</v>
+        <v>2.811882025863321</v>
       </c>
       <c r="F2" t="n">
-        <v>2.755809174796953</v>
+        <v>5.479442319290094</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9290627965976143</v>
+        <v>0.6877068367595487</v>
       </c>
       <c r="H2" t="n">
-        <v>3.475919113707131</v>
+        <v>6.105778045634129</v>
       </c>
       <c r="I2" t="n">
-        <v>1.840847984937388</v>
+        <v>3.386857071797398</v>
       </c>
       <c r="J2" t="n">
-        <v>3.440295102101322</v>
+        <v>8.13895113561578</v>
       </c>
       <c r="K2" t="n">
-        <v>0.8988599585985897</v>
+        <v>0.4632597768045376</v>
       </c>
     </row>
     <row r="3">
@@ -545,31 +545,31 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>169</v>
+        <v>234</v>
       </c>
       <c r="D3" t="n">
-        <v>1.080237388266095</v>
+        <v>1.075889289467704</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9836404595910582</v>
+        <v>0.9788690892706671</v>
       </c>
       <c r="F3" t="n">
-        <v>4.296788174711516</v>
+        <v>4.287674615856892</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8217338979659277</v>
+        <v>0.8224893067056587</v>
       </c>
       <c r="H3" t="n">
-        <v>1.372393407127368</v>
+        <v>1.37602279744084</v>
       </c>
       <c r="I3" t="n">
-        <v>1.163875279835391</v>
+        <v>1.166965024298628</v>
       </c>
       <c r="J3" t="n">
-        <v>4.810318338249981</v>
+        <v>4.804974921892738</v>
       </c>
       <c r="K3" t="n">
-        <v>0.9120531387836908</v>
+        <v>0.9122484172061645</v>
       </c>
     </row>
     <row r="4">
@@ -584,31 +584,31 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>169</v>
+        <v>234</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8267609583386537</v>
+        <v>0.8175246799918215</v>
       </c>
       <c r="E4" t="n">
-        <v>0.716515938221218</v>
+        <v>0.7064718312733543</v>
       </c>
       <c r="F4" t="n">
-        <v>3.362162388246943</v>
+        <v>3.35907652459286</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9528117569485496</v>
+        <v>0.9528983379297056</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6106872916793786</v>
+        <v>0.6130007144211314</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6974508930056273</v>
+        <v>0.7005126244861353</v>
       </c>
       <c r="J4" t="n">
-        <v>3.077447039614186</v>
+        <v>3.078282641691081</v>
       </c>
       <c r="K4" t="n">
-        <v>0.9453153141242143</v>
+        <v>0.9452856136353941</v>
       </c>
     </row>
     <row r="5">
@@ -623,31 +623,31 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>168</v>
+        <v>213</v>
       </c>
       <c r="D5" t="n">
-        <v>4.090822638647039</v>
+        <v>4.318793768964198</v>
       </c>
       <c r="E5" t="n">
-        <v>1.469152401165102</v>
+        <v>1.563576789484547</v>
       </c>
       <c r="F5" t="n">
-        <v>2.231269481513257</v>
+        <v>2.331451516613931</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9043404627666414</v>
+        <v>0.8955575617582829</v>
       </c>
       <c r="H5" t="n">
-        <v>4.039603029011061</v>
+        <v>4.096794646684014</v>
       </c>
       <c r="I5" t="n">
-        <v>1.543745650205762</v>
+        <v>1.554111766907109</v>
       </c>
       <c r="J5" t="n">
-        <v>2.189078855121269</v>
+        <v>2.26277240728757</v>
       </c>
       <c r="K5" t="n">
-        <v>0.9006571482808045</v>
+        <v>0.8938559733177291</v>
       </c>
     </row>
     <row r="6">
@@ -662,31 +662,31 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>171</v>
+        <v>276</v>
       </c>
       <c r="D6" t="n">
-        <v>2.412584472589698</v>
+        <v>2.402097920105152</v>
       </c>
       <c r="E6" t="n">
-        <v>3.667330521179721</v>
+        <v>3.650389086076817</v>
       </c>
       <c r="F6" t="n">
-        <v>7.981140072128379</v>
+        <v>7.955622016013482</v>
       </c>
       <c r="G6" t="n">
-        <v>0.83490126947832</v>
+        <v>0.835955320286343</v>
       </c>
       <c r="H6" t="n">
-        <v>1.404527208907398</v>
+        <v>1.464713478027484</v>
       </c>
       <c r="I6" t="n">
-        <v>1.395706172839505</v>
+        <v>1.421442873456793</v>
       </c>
       <c r="J6" t="n">
-        <v>5.678938424204445</v>
+        <v>5.668729123413043</v>
       </c>
       <c r="K6" t="n">
-        <v>0.9904842947984128</v>
+        <v>0.9905184777266125</v>
       </c>
     </row>
     <row r="7">
@@ -701,31 +701,31 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>168</v>
+        <v>213</v>
       </c>
       <c r="D7" t="n">
-        <v>3.806185782809625</v>
+        <v>3.754509445274856</v>
       </c>
       <c r="E7" t="n">
-        <v>1.233536460413938</v>
+        <v>1.215632205685921</v>
       </c>
       <c r="F7" t="n">
-        <v>2.109282641716446</v>
+        <v>2.062720484862587</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8242055587670627</v>
+        <v>0.8318811757593582</v>
       </c>
       <c r="H7" t="n">
-        <v>4.209301696521237</v>
+        <v>4.223334198062059</v>
       </c>
       <c r="I7" t="n">
-        <v>1.490988678325157</v>
+        <v>1.500969941677426</v>
       </c>
       <c r="J7" t="n">
-        <v>2.254351155379669</v>
+        <v>2.224354463036969</v>
       </c>
       <c r="K7" t="n">
-        <v>0.9046698091595458</v>
+        <v>0.9071898827126064</v>
       </c>
     </row>
   </sheetData>
@@ -749,11 +749,11 @@
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
     <col width="23" customWidth="1" min="8" max="8"/>
     <col width="19" customWidth="1" min="9" max="9"/>
     <col width="19" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="21" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -825,31 +825,31 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>69</v>
+        <v>198</v>
       </c>
       <c r="D2" t="n">
-        <v>3.501692361024815</v>
+        <v>6.05848867822634</v>
       </c>
       <c r="E2" t="n">
-        <v>1.722225655240091</v>
+        <v>2.679601366339635</v>
       </c>
       <c r="F2" t="n">
-        <v>2.768729867666459</v>
+        <v>5.339435070393012</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9283960548792013</v>
+        <v>0.7034619844418862</v>
       </c>
       <c r="H2" t="n">
-        <v>3.447852956093874</v>
+        <v>6.264011727644167</v>
       </c>
       <c r="I2" t="n">
-        <v>1.839286091604038</v>
+        <v>3.465673343407024</v>
       </c>
       <c r="J2" t="n">
-        <v>3.404496657355129</v>
+        <v>8.170810627537394</v>
       </c>
       <c r="K2" t="n">
-        <v>0.9009538595396125</v>
+        <v>0.4590494702010691</v>
       </c>
     </row>
     <row r="3">
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>90</v>
+        <v>229</v>
       </c>
       <c r="D3" t="n">
-        <v>2.346931442357257</v>
+        <v>8.244174327492388</v>
       </c>
       <c r="E3" t="n">
-        <v>2.305160486326509</v>
+        <v>8.262480584012122</v>
       </c>
       <c r="F3" t="n">
-        <v>4.642258055490738</v>
+        <v>12.04330344361514</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7919156409714565</v>
+        <v>-0.2911028129581079</v>
       </c>
       <c r="H3" t="n">
-        <v>2.33533295308859</v>
+        <v>12.52375367457808</v>
       </c>
       <c r="I3" t="n">
-        <v>2.09420220552992</v>
+        <v>12.86364438697415</v>
       </c>
       <c r="J3" t="n">
-        <v>5.147582401407586</v>
+        <v>18.57570150683231</v>
       </c>
       <c r="K3" t="n">
-        <v>0.8992884400653057</v>
+        <v>-0.3223620348064402</v>
       </c>
     </row>
     <row r="4">
@@ -903,31 +903,31 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>90</v>
+        <v>229</v>
       </c>
       <c r="D4" t="n">
-        <v>1.936903494559489</v>
+        <v>5.417944909182646</v>
       </c>
       <c r="E4" t="n">
-        <v>1.567633644343515</v>
+        <v>5.127193672709094</v>
       </c>
       <c r="F4" t="n">
-        <v>4.202708086615867</v>
+        <v>8.269477431121118</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9262681912387691</v>
+        <v>0.7108873313913491</v>
       </c>
       <c r="H4" t="n">
-        <v>2.239408662781647</v>
+        <v>6.486507480932811</v>
       </c>
       <c r="I4" t="n">
-        <v>2.837622642426907</v>
+        <v>8.186374988883136</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652194045140062</v>
+        <v>10.54438607873526</v>
       </c>
       <c r="K4" t="n">
-        <v>0.8750316061125879</v>
+        <v>0.3588665486066156</v>
       </c>
     </row>
     <row r="5">
@@ -942,31 +942,31 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>69</v>
+        <v>208</v>
       </c>
       <c r="D5" t="n">
-        <v>4.238571959461349</v>
+        <v>10.55492248548842</v>
       </c>
       <c r="E5" t="n">
-        <v>1.516569530483253</v>
+        <v>3.379175217776207</v>
       </c>
       <c r="F5" t="n">
-        <v>2.238807395827607</v>
+        <v>5.010023433893158</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9036930363532821</v>
+        <v>0.4544590404655644</v>
       </c>
       <c r="H5" t="n">
-        <v>4.30040395222705</v>
+        <v>7.511686904047209</v>
       </c>
       <c r="I5" t="n">
-        <v>1.646964171250341</v>
+        <v>2.671366219442956</v>
       </c>
       <c r="J5" t="n">
-        <v>2.305944257556542</v>
+        <v>3.758669009569813</v>
       </c>
       <c r="K5" t="n">
-        <v>0.8897670525211819</v>
+        <v>0.7277478315778818</v>
       </c>
     </row>
     <row r="6">
@@ -981,31 +981,31 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>132</v>
+        <v>271</v>
       </c>
       <c r="D6" t="n">
-        <v>3.222090472477653</v>
+        <v>19.76406097356364</v>
       </c>
       <c r="E6" t="n">
-        <v>4.938827657538766</v>
+        <v>30.27459950936974</v>
       </c>
       <c r="F6" t="n">
-        <v>8.273559370524294</v>
+        <v>37.05595622095722</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8225816060696165</v>
+        <v>-2.52307734939347</v>
       </c>
       <c r="H6" t="n">
-        <v>20.54777679547323</v>
+        <v>14.82343687136343</v>
       </c>
       <c r="I6" t="n">
-        <v>9.430290892648204</v>
+        <v>16.69977506382963</v>
       </c>
       <c r="J6" t="n">
-        <v>12.42113967086908</v>
+        <v>28.36984551932682</v>
       </c>
       <c r="K6" t="n">
-        <v>0.9544771388351685</v>
+        <v>0.7613413653292103</v>
       </c>
     </row>
     <row r="7">
@@ -1020,31 +1020,31 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>69</v>
+        <v>208</v>
       </c>
       <c r="D7" t="n">
-        <v>4.158230568291292</v>
+        <v>8.358686897884775</v>
       </c>
       <c r="E7" t="n">
-        <v>1.337182294123551</v>
+        <v>2.677038225290983</v>
       </c>
       <c r="F7" t="n">
-        <v>2.071133559933018</v>
+        <v>3.814916194364496</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8305069898727634</v>
+        <v>0.4045796665847206</v>
       </c>
       <c r="H7" t="n">
-        <v>4.239258178453239</v>
+        <v>6.59874955990287</v>
       </c>
       <c r="I7" t="n">
-        <v>1.502540638105792</v>
+        <v>2.242960360791789</v>
       </c>
       <c r="J7" t="n">
-        <v>2.150702262421912</v>
+        <v>3.250476284606959</v>
       </c>
       <c r="K7" t="n">
-        <v>0.9132343321080806</v>
+        <v>0.8052767670392167</v>
       </c>
     </row>
   </sheetData>
@@ -1068,11 +1068,11 @@
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
     <col width="23" customWidth="1" min="8" max="8"/>
     <col width="19" customWidth="1" min="9" max="9"/>
     <col width="19" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="21" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1144,31 +1144,31 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>69</v>
+        <v>198</v>
       </c>
       <c r="D2" t="n">
-        <v>3.442178031301716</v>
+        <v>12.67904447374227</v>
       </c>
       <c r="E2" t="n">
-        <v>1.707441965132599</v>
+        <v>6.199859678247157</v>
       </c>
       <c r="F2" t="n">
-        <v>2.72254522952243</v>
+        <v>9.053472191828156</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9307649537783601</v>
+        <v>0.1474495234600094</v>
       </c>
       <c r="H2" t="n">
-        <v>3.509399379877545</v>
+        <v>14.89827152521508</v>
       </c>
       <c r="I2" t="n">
-        <v>1.878446300181587</v>
+        <v>8.374156805655712</v>
       </c>
       <c r="J2" t="n">
-        <v>3.476054852101562</v>
+        <v>12.32075573692778</v>
       </c>
       <c r="K2" t="n">
-        <v>0.8967464541495956</v>
+        <v>-0.2299910619096863</v>
       </c>
     </row>
     <row r="3">
@@ -1183,31 +1183,31 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>90</v>
+        <v>229</v>
       </c>
       <c r="D3" t="n">
-        <v>2.530532639110426</v>
+        <v>8.012625712616954</v>
       </c>
       <c r="E3" t="n">
-        <v>2.488818946565228</v>
+        <v>7.965410476549016</v>
       </c>
       <c r="F3" t="n">
-        <v>5.069029658409963</v>
+        <v>11.44105689872277</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7518978404406891</v>
+        <v>-0.1652037139806954</v>
       </c>
       <c r="H3" t="n">
-        <v>3.171957013040032</v>
+        <v>11.11757252065611</v>
       </c>
       <c r="I3" t="n">
-        <v>2.881007947430395</v>
+        <v>11.08684116555558</v>
       </c>
       <c r="J3" t="n">
-        <v>5.725848741114103</v>
+        <v>15.96858331402931</v>
       </c>
       <c r="K3" t="n">
-        <v>0.8753901278951386</v>
+        <v>0.02277920160870939</v>
       </c>
     </row>
     <row r="4">
@@ -1222,31 +1222,31 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>90</v>
+        <v>229</v>
       </c>
       <c r="D4" t="n">
-        <v>1.733123207504459</v>
+        <v>5.759259863862858</v>
       </c>
       <c r="E4" t="n">
-        <v>1.39760265235116</v>
+        <v>5.377330824484067</v>
       </c>
       <c r="F4" t="n">
-        <v>3.837274827912132</v>
+        <v>11.9102742084685</v>
       </c>
       <c r="G4" t="n">
-        <v>0.938532967589625</v>
+        <v>0.400271744693631</v>
       </c>
       <c r="H4" t="n">
-        <v>1.122891815055167</v>
+        <v>6.021769925483243</v>
       </c>
       <c r="I4" t="n">
-        <v>1.360446344679844</v>
+        <v>7.438204439875792</v>
       </c>
       <c r="J4" t="n">
-        <v>3.201513621959849</v>
+        <v>10.783571771579</v>
       </c>
       <c r="K4" t="n">
-        <v>0.9408172346219235</v>
+        <v>0.3294500951967373</v>
       </c>
     </row>
     <row r="5">
@@ -1261,31 +1261,31 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>69</v>
+        <v>208</v>
       </c>
       <c r="D5" t="n">
-        <v>4.228837825239769</v>
+        <v>9.792670650301922</v>
       </c>
       <c r="E5" t="n">
-        <v>1.493498170948233</v>
+        <v>3.047561809257031</v>
       </c>
       <c r="F5" t="n">
-        <v>2.204112165219101</v>
+        <v>4.714574207131379</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9066548822164839</v>
+        <v>0.516904713062379</v>
       </c>
       <c r="H5" t="n">
-        <v>4.46530894611712</v>
+        <v>7.531215584620392</v>
       </c>
       <c r="I5" t="n">
-        <v>1.728274721971049</v>
+        <v>2.668592610358417</v>
       </c>
       <c r="J5" t="n">
-        <v>2.324389837729373</v>
+        <v>3.876753823489376</v>
       </c>
       <c r="K5" t="n">
-        <v>0.887996460681294</v>
+        <v>0.7103726111456587</v>
       </c>
     </row>
     <row r="6">
@@ -1300,31 +1300,31 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>132</v>
+        <v>271</v>
       </c>
       <c r="D6" t="n">
-        <v>2.866764171025353</v>
+        <v>12.84559291283292</v>
       </c>
       <c r="E6" t="n">
-        <v>4.366497925683041</v>
+        <v>19.75635822675999</v>
       </c>
       <c r="F6" t="n">
-        <v>7.737802122944278</v>
+        <v>26.61372465755518</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8448152264237136</v>
+        <v>-0.8172615919632893</v>
       </c>
       <c r="H6" t="n">
-        <v>31.86163441122522</v>
+        <v>11.32169312369476</v>
       </c>
       <c r="I6" t="n">
-        <v>12.23543353844474</v>
+        <v>12.22954181132504</v>
       </c>
       <c r="J6" t="n">
-        <v>19.00859413144825</v>
+        <v>22.41959472589807</v>
       </c>
       <c r="K6" t="n">
-        <v>0.8933878614097266</v>
+        <v>0.8509545491074079</v>
       </c>
     </row>
     <row r="7">
@@ -1339,31 +1339,31 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>69</v>
+        <v>208</v>
       </c>
       <c r="D7" t="n">
-        <v>4.081126789681326</v>
+        <v>13.84199780817706</v>
       </c>
       <c r="E7" t="n">
-        <v>1.311888584674097</v>
+        <v>4.323162675903657</v>
       </c>
       <c r="F7" t="n">
-        <v>2.05073072280375</v>
+        <v>5.73075663185077</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8338299094592184</v>
+        <v>-0.3436234941615954</v>
       </c>
       <c r="H7" t="n">
-        <v>4.334639090003693</v>
+        <v>8.038243618227868</v>
       </c>
       <c r="I7" t="n">
-        <v>1.550395305534122</v>
+        <v>2.630714025191922</v>
       </c>
       <c r="J7" t="n">
-        <v>2.177137877910224</v>
+        <v>3.667494929248991</v>
       </c>
       <c r="K7" t="n">
-        <v>0.9110882419285601</v>
+        <v>0.7521078284119701</v>
       </c>
     </row>
   </sheetData>
@@ -1387,11 +1387,11 @@
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
     <col width="23" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
     <col width="19" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="21" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1463,31 +1463,31 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>158</v>
+        <v>198</v>
       </c>
       <c r="D2" t="n">
-        <v>3.471231035467674</v>
+        <v>6.153104165758873</v>
       </c>
       <c r="E2" t="n">
-        <v>1.726776719652155</v>
+        <v>2.811882025863321</v>
       </c>
       <c r="F2" t="n">
-        <v>2.755809174796953</v>
+        <v>5.479442319290094</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9290627965976143</v>
+        <v>0.6877068367595487</v>
       </c>
       <c r="H2" t="n">
-        <v>3.475919113707131</v>
+        <v>6.105778045634129</v>
       </c>
       <c r="I2" t="n">
-        <v>1.840847984937388</v>
+        <v>3.386857071797398</v>
       </c>
       <c r="J2" t="n">
-        <v>3.440295102101322</v>
+        <v>8.13895113561578</v>
       </c>
       <c r="K2" t="n">
-        <v>0.8988599585985897</v>
+        <v>0.4632597768045376</v>
       </c>
     </row>
     <row r="3">
@@ -1502,31 +1502,31 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>169</v>
+        <v>234</v>
       </c>
       <c r="D3" t="n">
-        <v>1.080237388266095</v>
+        <v>1.075889289467704</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9836404595910582</v>
+        <v>0.9788690892706671</v>
       </c>
       <c r="F3" t="n">
-        <v>4.296788174711516</v>
+        <v>4.287674615856892</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8217338979659277</v>
+        <v>0.8224893067056587</v>
       </c>
       <c r="H3" t="n">
-        <v>1.372393407127368</v>
+        <v>1.37602279744084</v>
       </c>
       <c r="I3" t="n">
-        <v>1.163875279835391</v>
+        <v>1.166965024298628</v>
       </c>
       <c r="J3" t="n">
-        <v>4.810318338249981</v>
+        <v>4.804974921892738</v>
       </c>
       <c r="K3" t="n">
-        <v>0.9120531387836908</v>
+        <v>0.9122484172061645</v>
       </c>
     </row>
     <row r="4">
@@ -1541,31 +1541,31 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>169</v>
+        <v>234</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8267609583386537</v>
+        <v>0.8175246799918215</v>
       </c>
       <c r="E4" t="n">
-        <v>0.716515938221218</v>
+        <v>0.7064718312733543</v>
       </c>
       <c r="F4" t="n">
-        <v>3.362162388246943</v>
+        <v>3.35907652459286</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9528117569485496</v>
+        <v>0.9528983379297056</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6106872916793786</v>
+        <v>0.6130007144211314</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6974508930056273</v>
+        <v>0.7005126244861353</v>
       </c>
       <c r="J4" t="n">
-        <v>3.077447039614186</v>
+        <v>3.078282641691081</v>
       </c>
       <c r="K4" t="n">
-        <v>0.9453153141242143</v>
+        <v>0.9452856136353941</v>
       </c>
     </row>
     <row r="5">
@@ -1580,31 +1580,31 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>168</v>
+        <v>213</v>
       </c>
       <c r="D5" t="n">
-        <v>4.090822638647039</v>
+        <v>4.318793768964198</v>
       </c>
       <c r="E5" t="n">
-        <v>1.469152401165102</v>
+        <v>1.563576789484547</v>
       </c>
       <c r="F5" t="n">
-        <v>2.231269481513257</v>
+        <v>2.331451516613931</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9043404627666414</v>
+        <v>0.8955575617582829</v>
       </c>
       <c r="H5" t="n">
-        <v>4.039603029011061</v>
+        <v>4.096794646684014</v>
       </c>
       <c r="I5" t="n">
-        <v>1.543745650205762</v>
+        <v>1.554111766907109</v>
       </c>
       <c r="J5" t="n">
-        <v>2.189078855121269</v>
+        <v>2.26277240728757</v>
       </c>
       <c r="K5" t="n">
-        <v>0.9006571482808045</v>
+        <v>0.8938559733177291</v>
       </c>
     </row>
     <row r="6">
@@ -1619,31 +1619,31 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>171</v>
+        <v>276</v>
       </c>
       <c r="D6" t="n">
-        <v>2.412584472589698</v>
+        <v>2.402097920105152</v>
       </c>
       <c r="E6" t="n">
-        <v>3.667330521179721</v>
+        <v>3.650389086076817</v>
       </c>
       <c r="F6" t="n">
-        <v>7.981140072128379</v>
+        <v>7.955622016013482</v>
       </c>
       <c r="G6" t="n">
-        <v>0.83490126947832</v>
+        <v>0.835955320286343</v>
       </c>
       <c r="H6" t="n">
-        <v>1.404527208907398</v>
+        <v>1.464713478027484</v>
       </c>
       <c r="I6" t="n">
-        <v>1.395706172839505</v>
+        <v>1.421442873456793</v>
       </c>
       <c r="J6" t="n">
-        <v>5.678938424204445</v>
+        <v>5.668729123413043</v>
       </c>
       <c r="K6" t="n">
-        <v>0.9904842947984128</v>
+        <v>0.9905184777266125</v>
       </c>
     </row>
     <row r="7">
@@ -1658,31 +1658,31 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>168</v>
+        <v>213</v>
       </c>
       <c r="D7" t="n">
-        <v>3.806185782809625</v>
+        <v>3.754509445274856</v>
       </c>
       <c r="E7" t="n">
-        <v>1.233536460413938</v>
+        <v>1.215632205685921</v>
       </c>
       <c r="F7" t="n">
-        <v>2.109282641716446</v>
+        <v>2.062720484862587</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8242055587670627</v>
+        <v>0.8318811757593582</v>
       </c>
       <c r="H7" t="n">
-        <v>4.209301696521237</v>
+        <v>4.223334198062059</v>
       </c>
       <c r="I7" t="n">
-        <v>1.490988678325157</v>
+        <v>1.500969941677426</v>
       </c>
       <c r="J7" t="n">
-        <v>2.254351155379669</v>
+        <v>2.224354463036969</v>
       </c>
       <c r="K7" t="n">
-        <v>0.9046698091595458</v>
+        <v>0.9071898827126064</v>
       </c>
     </row>
     <row r="8">
@@ -1697,31 +1697,31 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>69</v>
+        <v>198</v>
       </c>
       <c r="D8" t="n">
-        <v>3.501692361024815</v>
+        <v>6.05848867822634</v>
       </c>
       <c r="E8" t="n">
-        <v>1.722225655240091</v>
+        <v>2.679601366339635</v>
       </c>
       <c r="F8" t="n">
-        <v>2.768729867666459</v>
+        <v>5.339435070393012</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9283960548792013</v>
+        <v>0.7034619844418862</v>
       </c>
       <c r="H8" t="n">
-        <v>3.447852956093874</v>
+        <v>6.264011727644167</v>
       </c>
       <c r="I8" t="n">
-        <v>1.839286091604038</v>
+        <v>3.465673343407024</v>
       </c>
       <c r="J8" t="n">
-        <v>3.404496657355129</v>
+        <v>8.170810627537394</v>
       </c>
       <c r="K8" t="n">
-        <v>0.9009538595396125</v>
+        <v>0.4590494702010691</v>
       </c>
     </row>
     <row r="9">
@@ -1736,31 +1736,31 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>90</v>
+        <v>229</v>
       </c>
       <c r="D9" t="n">
-        <v>2.346931442357257</v>
+        <v>8.244174327492388</v>
       </c>
       <c r="E9" t="n">
-        <v>2.305160486326509</v>
+        <v>8.262480584012122</v>
       </c>
       <c r="F9" t="n">
-        <v>4.642258055490738</v>
+        <v>12.04330344361514</v>
       </c>
       <c r="G9" t="n">
-        <v>0.7919156409714565</v>
+        <v>-0.2911028129581079</v>
       </c>
       <c r="H9" t="n">
-        <v>2.33533295308859</v>
+        <v>12.52375367457808</v>
       </c>
       <c r="I9" t="n">
-        <v>2.09420220552992</v>
+        <v>12.86364438697415</v>
       </c>
       <c r="J9" t="n">
-        <v>5.147582401407586</v>
+        <v>18.57570150683231</v>
       </c>
       <c r="K9" t="n">
-        <v>0.8992884400653057</v>
+        <v>-0.3223620348064402</v>
       </c>
     </row>
     <row r="10">
@@ -1775,31 +1775,31 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>90</v>
+        <v>229</v>
       </c>
       <c r="D10" t="n">
-        <v>1.936903494559489</v>
+        <v>5.417944909182646</v>
       </c>
       <c r="E10" t="n">
-        <v>1.567633644343515</v>
+        <v>5.127193672709094</v>
       </c>
       <c r="F10" t="n">
-        <v>4.202708086615867</v>
+        <v>8.269477431121118</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9262681912387691</v>
+        <v>0.7108873313913491</v>
       </c>
       <c r="H10" t="n">
-        <v>2.239408662781647</v>
+        <v>6.486507480932811</v>
       </c>
       <c r="I10" t="n">
-        <v>2.837622642426907</v>
+        <v>8.186374988883136</v>
       </c>
       <c r="J10" t="n">
-        <v>4.652194045140062</v>
+        <v>10.54438607873526</v>
       </c>
       <c r="K10" t="n">
-        <v>0.8750316061125879</v>
+        <v>0.3588665486066156</v>
       </c>
     </row>
     <row r="11">
@@ -1814,31 +1814,31 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>69</v>
+        <v>208</v>
       </c>
       <c r="D11" t="n">
-        <v>4.238571959461349</v>
+        <v>10.55492248548842</v>
       </c>
       <c r="E11" t="n">
-        <v>1.516569530483253</v>
+        <v>3.379175217776207</v>
       </c>
       <c r="F11" t="n">
-        <v>2.238807395827607</v>
+        <v>5.010023433893158</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9036930363532821</v>
+        <v>0.4544590404655644</v>
       </c>
       <c r="H11" t="n">
-        <v>4.30040395222705</v>
+        <v>7.511686904047209</v>
       </c>
       <c r="I11" t="n">
-        <v>1.646964171250341</v>
+        <v>2.671366219442956</v>
       </c>
       <c r="J11" t="n">
-        <v>2.305944257556542</v>
+        <v>3.758669009569813</v>
       </c>
       <c r="K11" t="n">
-        <v>0.8897670525211819</v>
+        <v>0.7277478315778818</v>
       </c>
     </row>
     <row r="12">
@@ -1853,31 +1853,31 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>132</v>
+        <v>271</v>
       </c>
       <c r="D12" t="n">
-        <v>3.222090472477653</v>
+        <v>19.76406097356364</v>
       </c>
       <c r="E12" t="n">
-        <v>4.938827657538766</v>
+        <v>30.27459950936974</v>
       </c>
       <c r="F12" t="n">
-        <v>8.273559370524294</v>
+        <v>37.05595622095722</v>
       </c>
       <c r="G12" t="n">
-        <v>0.8225816060696165</v>
+        <v>-2.52307734939347</v>
       </c>
       <c r="H12" t="n">
-        <v>20.54777679547323</v>
+        <v>14.82343687136343</v>
       </c>
       <c r="I12" t="n">
-        <v>9.430290892648204</v>
+        <v>16.69977506382963</v>
       </c>
       <c r="J12" t="n">
-        <v>12.42113967086908</v>
+        <v>28.36984551932682</v>
       </c>
       <c r="K12" t="n">
-        <v>0.9544771388351685</v>
+        <v>0.7613413653292103</v>
       </c>
     </row>
     <row r="13">
@@ -1892,31 +1892,31 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>69</v>
+        <v>208</v>
       </c>
       <c r="D13" t="n">
-        <v>4.158230568291292</v>
+        <v>8.358686897884775</v>
       </c>
       <c r="E13" t="n">
-        <v>1.337182294123551</v>
+        <v>2.677038225290983</v>
       </c>
       <c r="F13" t="n">
-        <v>2.071133559933018</v>
+        <v>3.814916194364496</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8305069898727634</v>
+        <v>0.4045796665847206</v>
       </c>
       <c r="H13" t="n">
-        <v>4.239258178453239</v>
+        <v>6.59874955990287</v>
       </c>
       <c r="I13" t="n">
-        <v>1.502540638105792</v>
+        <v>2.242960360791789</v>
       </c>
       <c r="J13" t="n">
-        <v>2.150702262421912</v>
+        <v>3.250476284606959</v>
       </c>
       <c r="K13" t="n">
-        <v>0.9132343321080806</v>
+        <v>0.8052767670392167</v>
       </c>
     </row>
     <row r="14">
@@ -1931,31 +1931,31 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>69</v>
+        <v>198</v>
       </c>
       <c r="D14" t="n">
-        <v>3.442178031301716</v>
+        <v>12.67904447374227</v>
       </c>
       <c r="E14" t="n">
-        <v>1.707441965132599</v>
+        <v>6.199859678247157</v>
       </c>
       <c r="F14" t="n">
-        <v>2.72254522952243</v>
+        <v>9.053472191828156</v>
       </c>
       <c r="G14" t="n">
-        <v>0.9307649537783601</v>
+        <v>0.1474495234600094</v>
       </c>
       <c r="H14" t="n">
-        <v>3.509399379877545</v>
+        <v>14.89827152521508</v>
       </c>
       <c r="I14" t="n">
-        <v>1.878446300181587</v>
+        <v>8.374156805655712</v>
       </c>
       <c r="J14" t="n">
-        <v>3.476054852101562</v>
+        <v>12.32075573692778</v>
       </c>
       <c r="K14" t="n">
-        <v>0.8967464541495956</v>
+        <v>-0.2299910619096863</v>
       </c>
     </row>
     <row r="15">
@@ -1970,31 +1970,31 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>90</v>
+        <v>229</v>
       </c>
       <c r="D15" t="n">
-        <v>2.530532639110426</v>
+        <v>8.012625712616954</v>
       </c>
       <c r="E15" t="n">
-        <v>2.488818946565228</v>
+        <v>7.965410476549016</v>
       </c>
       <c r="F15" t="n">
-        <v>5.069029658409963</v>
+        <v>11.44105689872277</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7518978404406891</v>
+        <v>-0.1652037139806954</v>
       </c>
       <c r="H15" t="n">
-        <v>3.171957013040032</v>
+        <v>11.11757252065611</v>
       </c>
       <c r="I15" t="n">
-        <v>2.881007947430395</v>
+        <v>11.08684116555558</v>
       </c>
       <c r="J15" t="n">
-        <v>5.725848741114103</v>
+        <v>15.96858331402931</v>
       </c>
       <c r="K15" t="n">
-        <v>0.8753901278951386</v>
+        <v>0.02277920160870939</v>
       </c>
     </row>
     <row r="16">
@@ -2009,31 +2009,31 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>90</v>
+        <v>229</v>
       </c>
       <c r="D16" t="n">
-        <v>1.733123207504459</v>
+        <v>5.759259863862858</v>
       </c>
       <c r="E16" t="n">
-        <v>1.39760265235116</v>
+        <v>5.377330824484067</v>
       </c>
       <c r="F16" t="n">
-        <v>3.837274827912132</v>
+        <v>11.9102742084685</v>
       </c>
       <c r="G16" t="n">
-        <v>0.938532967589625</v>
+        <v>0.400271744693631</v>
       </c>
       <c r="H16" t="n">
-        <v>1.122891815055167</v>
+        <v>6.021769925483243</v>
       </c>
       <c r="I16" t="n">
-        <v>1.360446344679844</v>
+        <v>7.438204439875792</v>
       </c>
       <c r="J16" t="n">
-        <v>3.201513621959849</v>
+        <v>10.783571771579</v>
       </c>
       <c r="K16" t="n">
-        <v>0.9408172346219235</v>
+        <v>0.3294500951967373</v>
       </c>
     </row>
     <row r="17">
@@ -2048,31 +2048,31 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>208</v>
       </c>
       <c r="D17" t="n">
-        <v>4.228837825239769</v>
+        <v>9.792670650301922</v>
       </c>
       <c r="E17" t="n">
-        <v>1.493498170948233</v>
+        <v>3.047561809257031</v>
       </c>
       <c r="F17" t="n">
-        <v>2.204112165219101</v>
+        <v>4.714574207131379</v>
       </c>
       <c r="G17" t="n">
-        <v>0.9066548822164839</v>
+        <v>0.516904713062379</v>
       </c>
       <c r="H17" t="n">
-        <v>4.46530894611712</v>
+        <v>7.531215584620392</v>
       </c>
       <c r="I17" t="n">
-        <v>1.728274721971049</v>
+        <v>2.668592610358417</v>
       </c>
       <c r="J17" t="n">
-        <v>2.324389837729373</v>
+        <v>3.876753823489376</v>
       </c>
       <c r="K17" t="n">
-        <v>0.887996460681294</v>
+        <v>0.7103726111456587</v>
       </c>
     </row>
     <row r="18">
@@ -2087,31 +2087,31 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>132</v>
+        <v>271</v>
       </c>
       <c r="D18" t="n">
-        <v>2.866764171025353</v>
+        <v>12.84559291283292</v>
       </c>
       <c r="E18" t="n">
-        <v>4.366497925683041</v>
+        <v>19.75635822675999</v>
       </c>
       <c r="F18" t="n">
-        <v>7.737802122944278</v>
+        <v>26.61372465755518</v>
       </c>
       <c r="G18" t="n">
-        <v>0.8448152264237136</v>
+        <v>-0.8172615919632893</v>
       </c>
       <c r="H18" t="n">
-        <v>31.86163441122522</v>
+        <v>11.32169312369476</v>
       </c>
       <c r="I18" t="n">
-        <v>12.23543353844474</v>
+        <v>12.22954181132504</v>
       </c>
       <c r="J18" t="n">
-        <v>19.00859413144825</v>
+        <v>22.41959472589807</v>
       </c>
       <c r="K18" t="n">
-        <v>0.8933878614097266</v>
+        <v>0.8509545491074079</v>
       </c>
     </row>
     <row r="19">
@@ -2126,31 +2126,31 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>69</v>
+        <v>208</v>
       </c>
       <c r="D19" t="n">
-        <v>4.081126789681326</v>
+        <v>13.84199780817706</v>
       </c>
       <c r="E19" t="n">
-        <v>1.311888584674097</v>
+        <v>4.323162675903657</v>
       </c>
       <c r="F19" t="n">
-        <v>2.05073072280375</v>
+        <v>5.73075663185077</v>
       </c>
       <c r="G19" t="n">
-        <v>0.8338299094592184</v>
+        <v>-0.3436234941615954</v>
       </c>
       <c r="H19" t="n">
-        <v>4.334639090003693</v>
+        <v>8.038243618227868</v>
       </c>
       <c r="I19" t="n">
-        <v>1.550395305534122</v>
+        <v>2.630714025191922</v>
       </c>
       <c r="J19" t="n">
-        <v>2.177137877910224</v>
+        <v>3.667494929248991</v>
       </c>
       <c r="K19" t="n">
-        <v>0.9110882419285601</v>
+        <v>0.7521078284119701</v>
       </c>
     </row>
   </sheetData>
